--- a/artfynd/A 53928-2025 artfynd.xlsx
+++ b/artfynd/A 53928-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356408</v>
+        <v>113611825</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Boliden, Vb</t>
+          <t>Boliden, Boliden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750830</v>
+        <v>750577</v>
       </c>
       <c r="R2" t="n">
-        <v>7200867</v>
+        <v>7201015</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,12 +759,18 @@
           <t>2023-09-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På låga av tall i tidigt nedbrytnibgsstadie i äldre produktionsskog av tall</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -770,75 +782,59 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
+          <t>Johanna Kühne, Amanda Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Naturvärdesinventering Eriksberg </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113611825</v>
+        <v>113356680</v>
       </c>
       <c r="B3" t="n">
-        <v>90279</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Boliden, Boliden, Vb</t>
+          <t>Boliden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750577</v>
+        <v>750948</v>
       </c>
       <c r="R3" t="n">
-        <v>7201015</v>
+        <v>7200794</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,18 +866,12 @@
           <t>2023-09-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På låga av tall i tidigt nedbrytnibgsstadie i äldre produktionsskog av tall</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,48 +883,43 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Amanda Johansson</t>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering Eriksberg </t>
+          <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356407</v>
+        <v>113356292</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750895</v>
+        <v>750645</v>
       </c>
       <c r="R4" t="n">
-        <v>7200797</v>
+        <v>7201022</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sågs flygande och hackande på träd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,37 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356658</v>
+        <v>113356405</v>
       </c>
       <c r="B5" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750581</v>
+        <v>750638</v>
       </c>
       <c r="R5" t="n">
-        <v>7201413</v>
+        <v>7201023</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,12 +1065,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,37 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356680</v>
+        <v>113356406</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1156,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750948</v>
+        <v>750979</v>
       </c>
       <c r="R6" t="n">
-        <v>7200794</v>
+        <v>7200688</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,15 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356405</v>
+        <v>113356407</v>
       </c>
       <c r="B7" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750638</v>
+        <v>750895</v>
       </c>
       <c r="R7" t="n">
-        <v>7201023</v>
+        <v>7200797</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,15 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356406</v>
+        <v>113356408</v>
       </c>
       <c r="B8" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750979</v>
+        <v>750830</v>
       </c>
       <c r="R8" t="n">
-        <v>7200688</v>
+        <v>7200867</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,117 +1397,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>113356292</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Boliden, Vb</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>750645</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7201022</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Skellefteå socken</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Sågs flygande och hackande på träd</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Johanna Kühne</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
         <is>
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 53928-2025 artfynd.xlsx
+++ b/artfynd/A 53928-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
           <t xml:space="preserve">Naturvärdesinventering Eriksberg </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113611825</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356680</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356292</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356405</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356406</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356407</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,8 +1436,22 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113356408</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>